--- a/data/Rating-Dimensions.xlsx
+++ b/data/Rating-Dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mariambzd\repos\bibMining\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0210C924-E5C7-437F-A7BC-815CC54E1BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632F6626-7FD2-4F5C-B57A-96C19DA56F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="740" xr2:uid="{7AB21B45-162E-4196-9590-DF417A04CC1D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="740" activeTab="3" xr2:uid="{7AB21B45-162E-4196-9590-DF417A04CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="163">
   <si>
     <t>Id</t>
   </si>
@@ -951,6 +951,7 @@
     <col min="2" max="2" width="42.33203125" customWidth="1"/>
     <col min="3" max="3" width="23.77734375" customWidth="1"/>
     <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -983,6 +984,9 @@
       <c r="D2" t="s">
         <v>53</v>
       </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -997,6 +1001,9 @@
       <c r="D3" t="s">
         <v>56</v>
       </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1011,6 +1018,9 @@
       <c r="D4" t="s">
         <v>57</v>
       </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1025,6 +1035,9 @@
       <c r="D5" t="s">
         <v>48</v>
       </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1039,6 +1052,9 @@
       <c r="D6" t="s">
         <v>48</v>
       </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1053,6 +1069,9 @@
       <c r="D7" t="s">
         <v>48</v>
       </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -1067,6 +1086,9 @@
       <c r="D8" t="s">
         <v>48</v>
       </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1081,6 +1103,9 @@
       <c r="D9" t="s">
         <v>57</v>
       </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1095,6 +1120,9 @@
       <c r="D10" t="s">
         <v>53</v>
       </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1109,6 +1137,9 @@
       <c r="D11" t="s">
         <v>56</v>
       </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1123,6 +1154,9 @@
       <c r="D12" t="s">
         <v>56</v>
       </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -1137,6 +1171,9 @@
       <c r="D13" t="s">
         <v>53</v>
       </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -1151,6 +1188,9 @@
       <c r="D14" t="s">
         <v>53</v>
       </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -1165,6 +1205,9 @@
       <c r="D15" t="s">
         <v>53</v>
       </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -1179,8 +1222,11 @@
       <c r="D16" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
@@ -1193,8 +1239,11 @@
       <c r="D17" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
@@ -1207,8 +1256,11 @@
       <c r="D18" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -1221,8 +1273,11 @@
       <c r="D19" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>6</v>
       </c>
@@ -1235,8 +1290,11 @@
       <c r="D20" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>6</v>
       </c>
@@ -1249,8 +1307,11 @@
       <c r="D21" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>6</v>
       </c>
@@ -1263,8 +1324,11 @@
       <c r="D22" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>6</v>
       </c>
@@ -1277,8 +1341,11 @@
       <c r="D23" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -1291,8 +1358,11 @@
       <c r="D24" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>6</v>
       </c>
@@ -1305,8 +1375,11 @@
       <c r="D25" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -1319,8 +1392,11 @@
       <c r="D26" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>13</v>
       </c>
@@ -1333,8 +1409,11 @@
       <c r="D27" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>13</v>
       </c>
@@ -1347,8 +1426,11 @@
       <c r="D28" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>13</v>
       </c>
@@ -1361,8 +1443,11 @@
       <c r="D29" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>13</v>
       </c>
@@ -1375,8 +1460,11 @@
       <c r="D30" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>13</v>
       </c>
@@ -1389,8 +1477,11 @@
       <c r="D31" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>13</v>
       </c>
@@ -1403,8 +1494,11 @@
       <c r="D32" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>13</v>
       </c>
@@ -1415,10 +1509,13 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="E33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>13</v>
       </c>
@@ -1431,8 +1528,11 @@
       <c r="D34" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>13</v>
       </c>
@@ -1445,8 +1545,11 @@
       <c r="D35" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>13</v>
       </c>
@@ -1459,8 +1562,11 @@
       <c r="D36" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>13</v>
       </c>
@@ -1473,8 +1579,11 @@
       <c r="D37" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>13</v>
       </c>
@@ -1487,8 +1596,11 @@
       <c r="D38" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>13</v>
       </c>
@@ -1501,8 +1613,11 @@
       <c r="D39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>13</v>
       </c>
@@ -1515,8 +1630,11 @@
       <c r="D40" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>13</v>
       </c>
@@ -1529,8 +1647,11 @@
       <c r="D41" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>13</v>
       </c>
@@ -1543,8 +1664,11 @@
       <c r="D42" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>13</v>
       </c>
@@ -1557,8 +1681,11 @@
       <c r="D43" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>13</v>
       </c>
@@ -1571,8 +1698,11 @@
       <c r="D44" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>13</v>
       </c>
@@ -1585,8 +1715,11 @@
       <c r="D45" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>13</v>
       </c>
@@ -1599,8 +1732,11 @@
       <c r="D46" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>13</v>
       </c>
@@ -1613,8 +1749,11 @@
       <c r="D47" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>27</v>
       </c>
@@ -1627,8 +1766,11 @@
       <c r="D48" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>27</v>
       </c>
@@ -1641,8 +1783,11 @@
       <c r="D49" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>27</v>
       </c>
@@ -1655,8 +1800,11 @@
       <c r="D50" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>27</v>
       </c>
@@ -1669,8 +1817,11 @@
       <c r="D51" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>27</v>
       </c>
@@ -1683,8 +1834,11 @@
       <c r="D52" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>27</v>
       </c>
@@ -1697,8 +1851,11 @@
       <c r="D53" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>27</v>
       </c>
@@ -1711,8 +1868,11 @@
       <c r="D54" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>27</v>
       </c>
@@ -1725,8 +1885,11 @@
       <c r="D55" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E55" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>27</v>
       </c>
@@ -1739,8 +1902,11 @@
       <c r="D56" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>27</v>
       </c>
@@ -1753,8 +1919,11 @@
       <c r="D57" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E57" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>27</v>
       </c>
@@ -1767,8 +1936,11 @@
       <c r="D58" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>27</v>
       </c>
@@ -1781,8 +1953,11 @@
       <c r="D59" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>27</v>
       </c>
@@ -1795,8 +1970,11 @@
       <c r="D60" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E60" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>27</v>
       </c>
@@ -1809,8 +1987,11 @@
       <c r="D61" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>27</v>
       </c>
@@ -1823,8 +2004,11 @@
       <c r="D62" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>27</v>
       </c>
@@ -1837,8 +2021,11 @@
       <c r="D63" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E63" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>27</v>
       </c>
@@ -1851,8 +2038,11 @@
       <c r="D64" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>27</v>
       </c>
@@ -1865,8 +2055,11 @@
       <c r="D65" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>27</v>
       </c>
@@ -1879,8 +2072,11 @@
       <c r="D66" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>27</v>
       </c>
@@ -1893,8 +2089,11 @@
       <c r="D67" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>27</v>
       </c>
@@ -1907,8 +2106,11 @@
       <c r="D68" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>27</v>
       </c>
@@ -1921,8 +2123,11 @@
       <c r="D69" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>27</v>
       </c>
@@ -1935,8 +2140,11 @@
       <c r="D70" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E70" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>27</v>
       </c>
@@ -1949,8 +2157,11 @@
       <c r="D71" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>27</v>
       </c>
@@ -1963,8 +2174,11 @@
       <c r="D72" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>27</v>
       </c>
@@ -1977,8 +2191,11 @@
       <c r="D73" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>27</v>
       </c>
@@ -1991,8 +2208,11 @@
       <c r="D74" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>27</v>
       </c>
@@ -2005,8 +2225,11 @@
       <c r="D75" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>27</v>
       </c>
@@ -2019,8 +2242,11 @@
       <c r="D76" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>27</v>
       </c>
@@ -2033,8 +2259,11 @@
       <c r="D77" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>27</v>
       </c>
@@ -2047,8 +2276,11 @@
       <c r="D78" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>27</v>
       </c>
@@ -2061,8 +2293,11 @@
       <c r="D79" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>27</v>
       </c>
@@ -2075,8 +2310,11 @@
       <c r="D80" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E80" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>27</v>
       </c>
@@ -2089,8 +2327,11 @@
       <c r="D81" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E81" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>27</v>
       </c>
@@ -2103,8 +2344,11 @@
       <c r="D82" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E82" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>27</v>
       </c>
@@ -2117,8 +2361,11 @@
       <c r="D83" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E83" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>27</v>
       </c>
@@ -2131,8 +2378,11 @@
       <c r="D84" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E84" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>27</v>
       </c>
@@ -2145,8 +2395,11 @@
       <c r="D85" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E85" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>28</v>
       </c>
@@ -2159,8 +2412,11 @@
       <c r="D86" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E86" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>28</v>
       </c>
@@ -2173,8 +2429,11 @@
       <c r="D87" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E87" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>28</v>
       </c>
@@ -2187,8 +2446,11 @@
       <c r="D88" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E88" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>28</v>
       </c>
@@ -2201,8 +2463,11 @@
       <c r="D89" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E89" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>28</v>
       </c>
@@ -2215,8 +2480,11 @@
       <c r="D90" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E90" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>28</v>
       </c>
@@ -2229,8 +2497,11 @@
       <c r="D91" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E91" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>28</v>
       </c>
@@ -2243,8 +2514,11 @@
       <c r="D92" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E92" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>28</v>
       </c>
@@ -2257,8 +2531,11 @@
       <c r="D93" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E93" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>28</v>
       </c>
@@ -2271,8 +2548,11 @@
       <c r="D94" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E94" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>28</v>
       </c>
@@ -2285,8 +2565,11 @@
       <c r="D95" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E95" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>28</v>
       </c>
@@ -2299,8 +2582,11 @@
       <c r="D96" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>28</v>
       </c>
@@ -2313,8 +2599,11 @@
       <c r="D97" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>28</v>
       </c>
@@ -2327,8 +2616,11 @@
       <c r="D98" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E98" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>28</v>
       </c>
@@ -2341,8 +2633,11 @@
       <c r="D99" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E99" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>28</v>
       </c>
@@ -2355,8 +2650,11 @@
       <c r="D100" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E100" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>28</v>
       </c>
@@ -2369,8 +2667,11 @@
       <c r="D101" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E101" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>28</v>
       </c>
@@ -2383,8 +2684,11 @@
       <c r="D102" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E102" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>28</v>
       </c>
@@ -2397,8 +2701,11 @@
       <c r="D103" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E103" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>28</v>
       </c>
@@ -2411,8 +2718,11 @@
       <c r="D104" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E104" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>28</v>
       </c>
@@ -2425,8 +2735,11 @@
       <c r="D105" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E105" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>28</v>
       </c>
@@ -2439,8 +2752,11 @@
       <c r="D106" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E106" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>28</v>
       </c>
@@ -2453,8 +2769,11 @@
       <c r="D107" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E107" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>28</v>
       </c>
@@ -2467,8 +2786,11 @@
       <c r="D108" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E108" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>28</v>
       </c>
@@ -2481,8 +2803,11 @@
       <c r="D109" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E109" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>28</v>
       </c>
@@ -2495,8 +2820,11 @@
       <c r="D110" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E110" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>28</v>
       </c>
@@ -2509,8 +2837,11 @@
       <c r="D111" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E111" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>28</v>
       </c>
@@ -2523,8 +2854,11 @@
       <c r="D112" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E112" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>28</v>
       </c>
@@ -2537,8 +2871,11 @@
       <c r="D113" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E113" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>28</v>
       </c>
@@ -2549,6 +2886,9 @@
         <v>1</v>
       </c>
       <c r="D114" t="s">
+        <v>57</v>
+      </c>
+      <c r="E114" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2666,6 +3006,9 @@
       <c r="D2" t="s">
         <v>57</v>
       </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -2680,6 +3023,9 @@
       <c r="D3" t="s">
         <v>57</v>
       </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -2693,6 +3039,9 @@
       </c>
       <c r="D4" t="s">
         <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2708,6 +3057,9 @@
       <c r="D5" t="s">
         <v>57</v>
       </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -2722,6 +3074,9 @@
       <c r="D6" t="s">
         <v>48</v>
       </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -2736,6 +3091,9 @@
       <c r="D7" t="s">
         <v>48</v>
       </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -2750,6 +3108,9 @@
       <c r="D8" t="s">
         <v>48</v>
       </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -2764,6 +3125,9 @@
       <c r="D9" t="s">
         <v>54</v>
       </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -2778,6 +3142,9 @@
       <c r="D10" t="s">
         <v>56</v>
       </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -2792,6 +3159,9 @@
       <c r="D11" t="s">
         <v>53</v>
       </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -2806,6 +3176,9 @@
       <c r="D12" t="s">
         <v>54</v>
       </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -2820,6 +3193,9 @@
       <c r="D13" t="s">
         <v>57</v>
       </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -2834,6 +3210,9 @@
       <c r="D14" t="s">
         <v>54</v>
       </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -2848,6 +3227,9 @@
       <c r="D15" t="s">
         <v>54</v>
       </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -2862,8 +3244,11 @@
       <c r="D16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
@@ -2876,8 +3261,11 @@
       <c r="D17" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>23</v>
       </c>
@@ -2890,8 +3278,11 @@
       <c r="D18" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2904,8 +3295,11 @@
       <c r="D19" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2916,6 +3310,9 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2929,6 +3326,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97154098-E534-4AC6-AD14-BEB7DBBE2E31}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="51.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2960,6 +3360,9 @@
       <c r="D2" t="s">
         <v>57</v>
       </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -2974,6 +3377,9 @@
       <c r="D3" t="s">
         <v>48</v>
       </c>
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -2988,6 +3394,9 @@
       <c r="D4" t="s">
         <v>48</v>
       </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -3002,6 +3411,9 @@
       <c r="D5" t="s">
         <v>48</v>
       </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -3016,6 +3428,9 @@
       <c r="D6" t="s">
         <v>53</v>
       </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -3030,6 +3445,9 @@
       <c r="D7" t="s">
         <v>48</v>
       </c>
+      <c r="E7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -3044,6 +3462,9 @@
       <c r="D8" t="s">
         <v>52</v>
       </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -3056,6 +3477,9 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
         <v>52</v>
       </c>
     </row>
